--- a/public/exports-60-250-with-coowners/29189803.xlsx
+++ b/public/exports-60-250-with-coowners/29189803.xlsx
@@ -8366,40 +8366,40 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strynøvej 8</t>
+          <t xml:space="preserve">Novrupvej 47</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5119870</t>
+          <t xml:space="preserve">5746884</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100102885</t>
+          <t xml:space="preserve">200014518</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Jessen Rådg. ing. FRI</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-11-03</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8456,11 +8456,11 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J113">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8516,40 +8516,40 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Novrupvej 47</t>
+          <t xml:space="preserve">Skolevej 35A</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6731</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5746884</t>
+          <t xml:space="preserve">5133594</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014518</t>
+          <t xml:space="preserve">200015289</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2019-06-18</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 35A</t>
+          <t xml:space="preserve">Skolevej 35D</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
@@ -8666,22 +8666,22 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 35D</t>
+          <t xml:space="preserve">Højvangshaven 12</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6731</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133594</t>
+          <t xml:space="preserve">7497842</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J116">
@@ -8689,17 +8689,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015289</t>
+          <t xml:space="preserve">200019061</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-18</t>
+          <t xml:space="preserve">2019-08-21</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangshaven 12</t>
+          <t xml:space="preserve">Højvangshaven 6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J117">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangshaven 6</t>
+          <t xml:space="preserve">Ribegade 149</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">7497842</t>
+          <t xml:space="preserve">7976965</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019061</t>
+          <t xml:space="preserve">200021276</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-21</t>
+          <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ribegade 149</t>
+          <t xml:space="preserve">Bjarkesgade 14</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7976965</t>
+          <t xml:space="preserve">5734841</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,21 +8910,21 @@
         </is>
       </c>
       <c r="J119">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021276</t>
+          <t xml:space="preserve">200021450</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-29</t>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,35 +8966,35 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjarkesgade 14</t>
+          <t xml:space="preserve">Gabelsvej 8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5734841</t>
+          <t xml:space="preserve">9671465</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021450</t>
+          <t xml:space="preserve">200021461</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabelsvej 8</t>
+          <t xml:space="preserve">Idræts Alle 12A</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J121">
-        <v>64</v>
+        <v>232</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9116,35 +9116,35 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 12A</t>
+          <t xml:space="preserve">Jernbanegade 47</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">9671465</t>
+          <t xml:space="preserve">8038805</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021461</t>
+          <t xml:space="preserve">200021480</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 47</t>
+          <t xml:space="preserve">Landlystvej 7A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038805</t>
+          <t xml:space="preserve">5108524</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,16 +9210,16 @@
         </is>
       </c>
       <c r="J123">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021480</t>
+          <t xml:space="preserve">200021574</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landlystvej 7A</t>
+          <t xml:space="preserve">Neptunvej 29</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5108524</t>
+          <t xml:space="preserve">5121097</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,16 +9285,16 @@
         </is>
       </c>
       <c r="J124">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021574</t>
+          <t xml:space="preserve">200021474</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neptunvej 29</t>
+          <t xml:space="preserve">Ålykken 71</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5121097</t>
+          <t xml:space="preserve">5119276</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021474</t>
+          <t xml:space="preserve">100136130</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykken 71</t>
+          <t xml:space="preserve">Gravlundvej 1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,20 +9426,20 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5119276</t>
+          <t xml:space="preserve">9061698</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">100136130</t>
+          <t xml:space="preserve">200025356</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,40 +9491,40 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gravlundvej 1</t>
+          <t xml:space="preserve">Vestre Lufthavnsvej 27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061698</t>
+          <t xml:space="preserve">8865861</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025356</t>
+          <t xml:space="preserve">100147076</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rådgivende ingeniørfirma FRI Poul Skærbæk</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-11</t>
+          <t xml:space="preserve">2020-01-20</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,40 +9566,40 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Lufthavnsvej 27</t>
+          <t xml:space="preserve">Grønningen 2G</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8865861</t>
+          <t xml:space="preserve">5046168</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J128">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100147076</t>
+          <t xml:space="preserve">200028555</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende ingeniørfirma FRI Poul Skærbæk</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-20</t>
+          <t xml:space="preserve">2020-02-26</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 2G</t>
+          <t xml:space="preserve">Storegade 307</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5046168</t>
+          <t xml:space="preserve">9433154</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028555</t>
+          <t xml:space="preserve">100151920</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-26</t>
+          <t xml:space="preserve">2020-03-12</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 307</t>
+          <t xml:space="preserve">Sønderhedevej 23</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9433154</t>
+          <t xml:space="preserve">9222849</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151920</t>
+          <t xml:space="preserve">100151931</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderhedevej 23</t>
+          <t xml:space="preserve">Søndre Novrupvej 11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222849</t>
+          <t xml:space="preserve">9475419</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151931</t>
+          <t xml:space="preserve">100151921</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Novrupvej 11</t>
+          <t xml:space="preserve">Tarp Byvej 6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9475419</t>
+          <t xml:space="preserve">5111046</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151921</t>
+          <t xml:space="preserve">100151928</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,40 +9941,40 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarp Byvej 6</t>
+          <t xml:space="preserve">Solgårdsvej 6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111046</t>
+          <t xml:space="preserve">8395247</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J133">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151928</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-12</t>
+          <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,30 +10016,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 6</t>
+          <t xml:space="preserve">Skovkanten 12</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8395247</t>
+          <t xml:space="preserve">5738607</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200030925</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-19</t>
+          <t xml:space="preserve">2020-04-29</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 12</t>
+          <t xml:space="preserve">Skovkanten 14</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738607</t>
+          <t xml:space="preserve">5738606</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030925</t>
+          <t xml:space="preserve">200030924</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 14</t>
+          <t xml:space="preserve">Skovkanten 16</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738606</t>
+          <t xml:space="preserve">5738605</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030924</t>
+          <t xml:space="preserve">200030920</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 16</t>
+          <t xml:space="preserve">Skovkanten 18</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738605</t>
+          <t xml:space="preserve">5738604</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030920</t>
+          <t xml:space="preserve">200030923</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 18</t>
+          <t xml:space="preserve">Skovkanten 22</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738604</t>
+          <t xml:space="preserve">5738603</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030923</t>
+          <t xml:space="preserve">200030922</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 22</t>
+          <t xml:space="preserve">Skovkanten 4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738603</t>
+          <t xml:space="preserve">5738609</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030922</t>
+          <t xml:space="preserve">200030921</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 4</t>
+          <t xml:space="preserve">Skovkanten 8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738609</t>
+          <t xml:space="preserve">5738608</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030921</t>
+          <t xml:space="preserve">200030926</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 8</t>
+          <t xml:space="preserve">Veldtoftevej 12</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738608</t>
+          <t xml:space="preserve">9475433</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,21 +10560,21 @@
         </is>
       </c>
       <c r="J141">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030926</t>
+          <t xml:space="preserve">100158184</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-29</t>
+          <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veldtoftevej 12</t>
+          <t xml:space="preserve">Østre Kjersingvej 21</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9475433</t>
+          <t xml:space="preserve">8388139</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158184</t>
+          <t xml:space="preserve">100158181</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kjersingvej 21</t>
+          <t xml:space="preserve">Stormgade 258</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388139</t>
+          <t xml:space="preserve">8388154</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158181</t>
+          <t xml:space="preserve">100158360</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-04</t>
+          <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormgade 258</t>
+          <t xml:space="preserve">Tradsborgvej 16</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6731</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388154</t>
+          <t xml:space="preserve">9243321</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158360</t>
+          <t xml:space="preserve">100158357</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tradsborgvej 16</t>
+          <t xml:space="preserve">Baggesens Alle 10</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6731</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9243321</t>
+          <t xml:space="preserve">5735054</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158357</t>
+          <t xml:space="preserve">200032449</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-05</t>
+          <t xml:space="preserve">2020-06-10</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baggesens Alle 10</t>
+          <t xml:space="preserve">Ølufvad Hovedvej 83</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5735054</t>
+          <t xml:space="preserve">5123806</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,16 +10935,16 @@
         </is>
       </c>
       <c r="J146">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032449</t>
+          <t xml:space="preserve">200032424</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -10991,40 +10991,40 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølufvad Hovedvej 83</t>
+          <t xml:space="preserve">Storegade 307</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5123806</t>
+          <t xml:space="preserve">9433154</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J147">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032424</t>
+          <t xml:space="preserve">200032892</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-10</t>
+          <t xml:space="preserve">2020-06-23</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,40 +11066,40 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 307</t>
+          <t xml:space="preserve">Kjærgårdsvej 9D</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">9433154</t>
+          <t xml:space="preserve">736932, 5052565</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J148">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032892</t>
+          <t xml:space="preserve">200033093</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-23</t>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,40 +11141,40 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgårdsvej 9D</t>
+          <t xml:space="preserve">Grønnegårdsvej 8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">736932, 5052565</t>
+          <t xml:space="preserve">5745295</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033093</t>
+          <t xml:space="preserve">200035324</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-08-16</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 8</t>
+          <t xml:space="preserve">Grådybparken 19</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5745295</t>
+          <t xml:space="preserve">5738772</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>221</v>
+        <v>129</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035324</t>
+          <t xml:space="preserve">200039948</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-16</t>
+          <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grådybparken 19</t>
+          <t xml:space="preserve">Tarp Byvej 85</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738772</t>
+          <t xml:space="preserve">10036827</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039948</t>
+          <t xml:space="preserve">200039947</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,30 +11366,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarp Byvej 85</t>
+          <t xml:space="preserve">Grønningen 3B</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">10036827</t>
+          <t xml:space="preserve">5046407</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039947</t>
+          <t xml:space="preserve">200040064</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-28</t>
+          <t xml:space="preserve">2020-10-29</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,40 +11441,40 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 3B</t>
+          <t xml:space="preserve">Birkekrattet 4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5046407</t>
+          <t xml:space="preserve">8725263</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040064</t>
+          <t xml:space="preserve">200052050</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-29</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,40 +11516,40 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkekrattet 4</t>
+          <t xml:space="preserve">Gabelsvej 8</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8725263</t>
+          <t xml:space="preserve">9671465</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J154">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052050</t>
+          <t xml:space="preserve">200059087</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2022-04-24</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,40 +11591,40 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabelsvej 8</t>
+          <t xml:space="preserve">Skads Byvej 93</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9671465</t>
+          <t xml:space="preserve">7912300</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059087</t>
+          <t xml:space="preserve">100266185</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">R arkitekter, Esbjerg</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-24</t>
+          <t xml:space="preserve">2022-04-26</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,40 +11666,40 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skads Byvej 93</t>
+          <t xml:space="preserve">Mukkerten 14</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912300</t>
+          <t xml:space="preserve">8042751</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J156">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">100266185</t>
+          <t xml:space="preserve">311051467</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">R arkitekter, Esbjerg</t>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-26</t>
+          <t xml:space="preserve">2024-04-30</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,40 +11741,40 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mukkerten 14</t>
+          <t xml:space="preserve">Skads Byvej 102</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042751</t>
+          <t xml:space="preserve">5748022</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311051467</t>
+          <t xml:space="preserve">311087026</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+          <t xml:space="preserve">R arkitekter, Esbjerg</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04-30</t>
+          <t xml:space="preserve">2024-12-08</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skads Byvej 102</t>
+          <t xml:space="preserve">Ole Rømers Vej 50</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5748022</t>
+          <t xml:space="preserve">7656815</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,31 +11835,31 @@
         </is>
       </c>
       <c r="J158">
-        <v>247</v>
+        <v>66</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087026</t>
+          <t xml:space="preserve">311359415</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">R arkitekter, Esbjerg</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-08</t>
+          <t xml:space="preserve">2029-02-13</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11891,17 +11891,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ole Rømers Vej 50</t>
+          <t xml:space="preserve">Måde Kirkevej 35</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">7656815</t>
+          <t xml:space="preserve">8948776</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="J159">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359415</t>
+          <t xml:space="preserve">311359647</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-13</t>
+          <t xml:space="preserve">2029-02-14</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,40 +11966,40 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Måde Kirkevej 35</t>
+          <t xml:space="preserve">Bygaden 43</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948776</t>
+          <t xml:space="preserve">5054539</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J160">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359647</t>
+          <t xml:space="preserve">311442081</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">BYGTEST ApS</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-14</t>
+          <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 43</t>
+          <t xml:space="preserve">Ringen 61E</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5054539</t>
+          <t xml:space="preserve">8388410</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,21 +12060,21 @@
         </is>
       </c>
       <c r="J161">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442101</t>
+          <t xml:space="preserve">311567887</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">BYGTEST ApS</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-08</t>
+          <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringen 61E</t>
+          <t xml:space="preserve">Ringen 61F</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,11 +12131,11 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringen 61F</t>
+          <t xml:space="preserve">Skolevej 32</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6731</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388410</t>
+          <t xml:space="preserve">5133969</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567887</t>
+          <t xml:space="preserve">311567884</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,30 +12266,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 32</t>
+          <t xml:space="preserve">Skrænten 120</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6731</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133969</t>
+          <t xml:space="preserve">5746415</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J164">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567884</t>
+          <t xml:space="preserve">311567883</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,30 +12341,30 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrænten 120</t>
+          <t xml:space="preserve">Kongeåvej 17</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6771</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5746415</t>
+          <t xml:space="preserve">5053434</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J165">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567883</t>
+          <t xml:space="preserve">311582274</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J166">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongeåvej 17</t>
+          <t xml:space="preserve">Kongeåvej 17A</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12506,15 +12506,15 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J167">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582274</t>
+          <t xml:space="preserve">311582276</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12561,35 +12561,35 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">561</t>
+          <t xml:space="preserve">540</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongeåvej 17A</t>
+          <t xml:space="preserve">Rendbjergvej 12</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6771</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5053434</t>
+          <t xml:space="preserve">5283241</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582276</t>
+          <t xml:space="preserve">311582270</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12656,15 +12656,15 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J169">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582270</t>
+          <t xml:space="preserve">311582271</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12711,35 +12711,35 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">540</t>
+          <t xml:space="preserve">561</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rendbjergvej 12</t>
+          <t xml:space="preserve">Bakkevej 2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5283241</t>
+          <t xml:space="preserve">5046638</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J170">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582271</t>
+          <t xml:space="preserve">311594111</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 2</t>
+          <t xml:space="preserve">Haulundvej 3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5046638</t>
+          <t xml:space="preserve">5752935</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J171">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594111</t>
+          <t xml:space="preserve">311594113</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12881,15 +12881,15 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J172">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594113</t>
+          <t xml:space="preserve">311594112</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haulundvej 3</t>
+          <t xml:space="preserve">Skolebakken 166</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5752935</t>
+          <t xml:space="preserve">5743760</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594112</t>
+          <t xml:space="preserve">311612678</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 166</t>
+          <t xml:space="preserve">Hjertingparken 200</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5743760</t>
+          <t xml:space="preserve">8388188</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J174">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612678</t>
+          <t xml:space="preserve">311623037</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-04</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,40 +13091,40 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjertingparken 200</t>
+          <t xml:space="preserve">Egedalvej 7C</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388188</t>
+          <t xml:space="preserve">9061836</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623037</t>
+          <t xml:space="preserve">311624660</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalvej 7C</t>
+          <t xml:space="preserve">Askekrattet 6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,30 +13176,30 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061836</t>
+          <t xml:space="preserve">5745656</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J176">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624660</t>
+          <t xml:space="preserve">311634690</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askekrattet 6</t>
+          <t xml:space="preserve">Askekrattet 8</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13256,11 +13256,11 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J177">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askekrattet 8</t>
+          <t xml:space="preserve">Vester Gjesingvej 30</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5745656</t>
+          <t xml:space="preserve">5109285</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J178">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311634690</t>
+          <t xml:space="preserve">311634671</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Gjesingvej 30</t>
+          <t xml:space="preserve">Grønlandsparken 300</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5109285</t>
+          <t xml:space="preserve">5110960</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311634671</t>
+          <t xml:space="preserve">311647854</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-11</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,40 +13466,40 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønlandsparken 300</t>
+          <t xml:space="preserve">Kvaglundparken 10</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5110960</t>
+          <t xml:space="preserve">313640</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647854</t>
+          <t xml:space="preserve">311653796</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kvaglundparken 10</t>
+          <t xml:space="preserve">Grønnegårdsvej 28A</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">313640</t>
+          <t xml:space="preserve">9433154</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,21 +13560,21 @@
         </is>
       </c>
       <c r="J181">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653796</t>
+          <t xml:space="preserve">311665868</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 28A</t>
+          <t xml:space="preserve">Grønnegårdsvej 28B</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J182">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665868</t>
+          <t xml:space="preserve">311665870</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 28B</t>
+          <t xml:space="preserve">Grønnegårdsvej 30A</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13706,15 +13706,15 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J183">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665870</t>
+          <t xml:space="preserve">311665854</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 30A</t>
+          <t xml:space="preserve">Grønnegårdsvej 30B</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13781,15 +13781,15 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J184">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665854</t>
+          <t xml:space="preserve">311665853</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 30B</t>
+          <t xml:space="preserve">Nørrebyvej 14</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9433154</t>
+          <t xml:space="preserve">5050770</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J185">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665853</t>
+          <t xml:space="preserve">311665859</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,40 +13916,40 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebyvej 14</t>
+          <t xml:space="preserve">Sorsigvej 10</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5050770</t>
+          <t xml:space="preserve">5751925</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J186">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665859</t>
+          <t xml:space="preserve">311672713</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-04-11</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,40 +13991,40 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorsigvej 10</t>
+          <t xml:space="preserve">Grønnegårdsvej 8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5751925</t>
+          <t xml:space="preserve">5745295</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311672713</t>
+          <t xml:space="preserve">311683882</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-11</t>
+          <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,17 +14066,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 8</t>
+          <t xml:space="preserve">Langliparken 7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5745295</t>
+          <t xml:space="preserve">5116465</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683882</t>
+          <t xml:space="preserve">311683873</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J189">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langliparken 7</t>
+          <t xml:space="preserve">Nør-Eng 4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5116465</t>
+          <t xml:space="preserve">5060108</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J190">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683873</t>
+          <t xml:space="preserve">311696702</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-30</t>
+          <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nør-Eng 4</t>
+          <t xml:space="preserve">Nør-Eng 6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J191">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nør-Eng 6</t>
+          <t xml:space="preserve">Seminarievej 23B</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,20 +14376,20 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5060108</t>
+          <t xml:space="preserve">5753446</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J192">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696702</t>
+          <t xml:space="preserve">311696670</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,40 +14441,40 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seminarievej 23B</t>
+          <t xml:space="preserve">Hovedvej A1 27</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5753446</t>
+          <t xml:space="preserve">5129039</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>245</v>
+        <v>112</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696670</t>
+          <t xml:space="preserve">311700903</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-26</t>
+          <t xml:space="preserve">2033-08-17</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvej A1 27</t>
+          <t xml:space="preserve">Fridtjof Nansens Vej 45</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129039</t>
+          <t xml:space="preserve">5109189</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,11 +14535,11 @@
         </is>
       </c>
       <c r="J194">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700903</t>
+          <t xml:space="preserve">311748048</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-17</t>
+          <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridtjof Nansens Vej 45</t>
+          <t xml:space="preserve">Ørnevænget 1</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5109189</t>
+          <t xml:space="preserve">5750798</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311748048</t>
+          <t xml:space="preserve">311748180</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevænget 1</t>
+          <t xml:space="preserve">Topsand 5</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5750798</t>
+          <t xml:space="preserve">5119158</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14685,11 +14685,11 @@
         </is>
       </c>
       <c r="J196">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311748180</t>
+          <t xml:space="preserve">311749185</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-26</t>
+          <t xml:space="preserve">2034-04-03</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,17 +14741,17 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topsand 5</t>
+          <t xml:space="preserve">Rolfsgade 63</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5119158</t>
+          <t xml:space="preserve">5736527</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14760,21 +14760,21 @@
         </is>
       </c>
       <c r="J197">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311749185</t>
+          <t xml:space="preserve">311751153</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-03</t>
+          <t xml:space="preserve">2034-04-11</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolfsgade 63</t>
+          <t xml:space="preserve">Rolfsgade 67</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5736527</t>
+          <t xml:space="preserve">5736586</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751153</t>
+          <t xml:space="preserve">311751314</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolfsgade 67</t>
+          <t xml:space="preserve">Bakkevej 6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,30 +14901,30 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5736586</t>
+          <t xml:space="preserve">5747038</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J199">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751314</t>
+          <t xml:space="preserve">311757225</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-11</t>
+          <t xml:space="preserve">2034-05-06</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 6</t>
+          <t xml:space="preserve">Skolebakken 86</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,20 +14976,20 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5747038</t>
+          <t xml:space="preserve">5743878</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J200">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757225</t>
+          <t xml:space="preserve">311757226</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,17 +15041,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 86</t>
+          <t xml:space="preserve">Stokbrovej 16</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5743878</t>
+          <t xml:space="preserve">5123396</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,11 +15060,11 @@
         </is>
       </c>
       <c r="J201">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757226</t>
+          <t xml:space="preserve">311758142</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-06</t>
+          <t xml:space="preserve">2034-05-08</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,30 +15116,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stokbrovej 16</t>
+          <t xml:space="preserve">Askekrattet 1</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5123396</t>
+          <t xml:space="preserve">8274789</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J202">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758142</t>
+          <t xml:space="preserve">311759421</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-08</t>
+          <t xml:space="preserve">2034-05-15</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askekrattet 1</t>
+          <t xml:space="preserve">Jupitervænget 57</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8274789</t>
+          <t xml:space="preserve">5117962</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759421</t>
+          <t xml:space="preserve">311759427</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervænget 57</t>
+          <t xml:space="preserve">Nørrebrogade 102</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117962</t>
+          <t xml:space="preserve">5741016</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J204">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759427</t>
+          <t xml:space="preserve">311759426</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebrogade 102</t>
+          <t xml:space="preserve">Darumvej 110</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5741016</t>
+          <t xml:space="preserve">7236586</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,11 +15360,11 @@
         </is>
       </c>
       <c r="J205">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759426</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-15</t>
+          <t xml:space="preserve">2034-05-16</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15401,12 +15401,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esbjerg Kommune</t>
+          <t xml:space="preserve">ESEBOLIG</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -15416,40 +15416,40 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darumvej 110</t>
+          <t xml:space="preserve">Hedelundvej 102</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7236586</t>
+          <t xml:space="preserve">501391, 501402, 5744392</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759943</t>
+          <t xml:space="preserve">311775351</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-16</t>
+          <t xml:space="preserve">2034-07-29</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 102</t>
+          <t xml:space="preserve">Hedelundvej 106</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">501391, 501402, 5744392</t>
+          <t xml:space="preserve">501408, 501409, 5744392</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J207">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 106</t>
+          <t xml:space="preserve">Hedelundvej 110</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">501408, 501409, 5744392</t>
+          <t xml:space="preserve">501410, 501411, 5744392</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J208">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 110</t>
+          <t xml:space="preserve">Hedelundvej 114</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,12 +15651,12 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">501410, 501411, 5744392</t>
+          <t xml:space="preserve">501412, 501413, 5744392</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J209">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 114</t>
+          <t xml:space="preserve">Hedelundvej 118</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,12 +15726,12 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">501412, 501413, 5744392</t>
+          <t xml:space="preserve">501392, 501414, 5744392</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J210">
@@ -15776,12 +15776,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESEBOLIG</t>
+          <t xml:space="preserve">Esbjerg Kommune</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 118</t>
+          <t xml:space="preserve">Hedelundvej 120</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,20 +15801,20 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">501392, 501414, 5744392</t>
+          <t xml:space="preserve">5744392</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J211">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311775351</t>
+          <t xml:space="preserve">311775354</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esbjerg Kommune</t>
+          <t xml:space="preserve">ESEBOLIG</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 120</t>
+          <t xml:space="preserve">Hedelundvej 126</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5744392</t>
+          <t xml:space="preserve">501393, 501394, 5744392</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J212">
-        <v>103</v>
+        <v>192</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311775354</t>
+          <t xml:space="preserve">311775351</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 126</t>
+          <t xml:space="preserve">Hedelundvej 130</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,12 +15951,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">501393, 501394, 5744392</t>
+          <t xml:space="preserve">501395, 501396, 5744392</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J213">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 130</t>
+          <t xml:space="preserve">Hedelundvej 134</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,12 +16026,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">501395, 501396, 5744392</t>
+          <t xml:space="preserve">501397, 501398, 5744392</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J214">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 134</t>
+          <t xml:space="preserve">Hedelundvej 138</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">501397, 501398, 5744392</t>
+          <t xml:space="preserve">501399, 501400, 5744392</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J215">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 138</t>
+          <t xml:space="preserve">Hedelundvej 142</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,12 +16176,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">501399, 501400, 5744392</t>
+          <t xml:space="preserve">501401, 501403, 5744392</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J216">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 142</t>
+          <t xml:space="preserve">Hedelundvej 146</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">501401, 501403, 5744392</t>
+          <t xml:space="preserve">501404, 501405, 5744392</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J217">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 146</t>
+          <t xml:space="preserve">Hedelundvej 150</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">501404, 501405, 5744392</t>
+          <t xml:space="preserve">501406, 501407, 5744392</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J218">
@@ -16376,12 +16376,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESEBOLIG</t>
+          <t xml:space="preserve">Esbjerg Kommune</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 150</t>
+          <t xml:space="preserve">John Tranums Vej 38</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,30 +16401,30 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">501406, 501407, 5744392</t>
+          <t xml:space="preserve">7872805</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J219">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311775351</t>
+          <t xml:space="preserve">311780599</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-29</t>
+          <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,30 +16466,30 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Tranums Vej 38</t>
+          <t xml:space="preserve">Tangevej 6H</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7872805</t>
+          <t xml:space="preserve">5749171</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J220">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780599</t>
+          <t xml:space="preserve">311802433</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-27</t>
+          <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,40 +16541,40 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangevej 6H</t>
+          <t xml:space="preserve">Astrupvej 2A</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5749171</t>
+          <t xml:space="preserve">5108659</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802433</t>
+          <t xml:space="preserve">311837308</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-13</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astrupvej 2A</t>
+          <t xml:space="preserve">Gjesinglund Alle 2</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,7 +16626,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5108659</t>
+          <t xml:space="preserve">7395397</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837308</t>
+          <t xml:space="preserve">311847384</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-08-05</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J223">
-        <v>240</v>
+        <v>124</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16766,40 +16766,40 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gjesinglund Alle 2</t>
+          <t xml:space="preserve">Guldagervej 98</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">7395397</t>
+          <t xml:space="preserve">1492153</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847384</t>
+          <t xml:space="preserve">311853987</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-05</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,17 +16841,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldagervej 98</t>
+          <t xml:space="preserve">Nørremarkvej 29</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492153</t>
+          <t xml:space="preserve">5049304</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,21 +16860,21 @@
         </is>
       </c>
       <c r="J225">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853987</t>
+          <t xml:space="preserve">311868109</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,30 +16916,30 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarkvej 29</t>
+          <t xml:space="preserve">Ravnsbjergvej 6</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5049304</t>
+          <t xml:space="preserve">8192368</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J226">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868109</t>
+          <t xml:space="preserve">311870754</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-13</t>
+          <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,30 +16991,30 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsbjergvej 6</t>
+          <t xml:space="preserve">Tarpgårdsvej 9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">8192368</t>
+          <t xml:space="preserve">5111073</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870754</t>
+          <t xml:space="preserve">311871125</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-28</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,17 +17066,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarpgårdsvej 9</t>
+          <t xml:space="preserve">Guldager Stationsvej 105</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111073</t>
+          <t xml:space="preserve">8388168</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -17085,11 +17085,11 @@
         </is>
       </c>
       <c r="J228">
-        <v>244</v>
+        <v>168</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871125</t>
+          <t xml:space="preserve">311874231</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-01</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17156,15 +17156,15 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J229">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874231</t>
+          <t xml:space="preserve">311874233</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17231,11 +17231,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J230">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -17291,40 +17291,40 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldager Stationsvej 105</t>
+          <t xml:space="preserve">Kastanie Alle 14</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388168</t>
+          <t xml:space="preserve">8410630</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J231">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874233</t>
+          <t xml:space="preserve">311916833</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 14</t>
+          <t xml:space="preserve">Kastanie Alle 3A</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17381,11 +17381,11 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J232">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 3A</t>
+          <t xml:space="preserve">Kastanie Alle 6A</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="J233">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 6A</t>
+          <t xml:space="preserve">Kastanie Alle 6C</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="J234">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 6C</t>
+          <t xml:space="preserve">Kastanie Alle 6E</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17606,11 +17606,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">79</t>
         </is>
       </c>
       <c r="J235">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 6E</t>
+          <t xml:space="preserve">Kastanie Alle 8A</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17681,11 +17681,11 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">79</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="J236">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 8A</t>
+          <t xml:space="preserve">Kastanie Alle 8C</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">78</t>
         </is>
       </c>
       <c r="J237">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 8C</t>
+          <t xml:space="preserve">Pile Alle 4</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17831,11 +17831,11 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J238">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -17891,40 +17891,40 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 4</t>
+          <t xml:space="preserve">Bakkevej 3</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410630</t>
+          <t xml:space="preserve">5747045</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J239">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916833</t>
+          <t xml:space="preserve">311919867</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-28</t>
+          <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,17 +17966,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 3</t>
+          <t xml:space="preserve">Plantagevej 35</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5747045</t>
+          <t xml:space="preserve">7254548</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="J240">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919867</t>
+          <t xml:space="preserve">311919928</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 35</t>
+          <t xml:space="preserve">Krebsens Kvarter 56A</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,30 +18051,30 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">7254548</t>
+          <t xml:space="preserve">8388213</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J241">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919928</t>
+          <t xml:space="preserve">311925681</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">STD Klima og Byggeri ApS</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-18</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krebsens Kvarter 56A</t>
+          <t xml:space="preserve">Strynøvej 8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,30 +18126,30 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388213</t>
+          <t xml:space="preserve">5119870</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925681</t>
+          <t xml:space="preserve">311930444</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD Klima og Byggeri ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
